--- a/Lista_Inmobiliarias_y_Telefonos_ICDE.xlsx
+++ b/Lista_Inmobiliarias_y_Telefonos_ICDE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\GitHub\Catalogo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E36DE5C-FD89-4356-9B91-EABB83691B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7E2FF6-8557-4A57-A3B3-365A8149747C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="6225" yWindow="15" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Inmobiliarias" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6413" uniqueCount="2803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6407" uniqueCount="2801">
   <si>
     <t>DIRECTORIO DE INMOBILIARIAS Y CONTACTOS - BASE DE DATOS ICDE</t>
   </si>
@@ -8424,12 +8424,6 @@
   </si>
   <si>
     <t>✅</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>3157872276 | 3114262158</t>
   </si>
 </sst>
 </file>
@@ -8832,7 +8826,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1048570"/>
+  <dimension ref="A1:D1048568"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
@@ -8888,22 +8882,22 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>2802</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>2800</v>
@@ -8912,10 +8906,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3182198358</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>2800</v>
@@ -8924,10 +8918,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="4">
-        <v>3182198358</v>
+        <v>49</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>2800</v>
@@ -8936,10 +8930,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>2800</v>
@@ -8948,10 +8942,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>2800</v>
@@ -8960,22 +8954,22 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>110</v>
+        <v>2791</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3103914892</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>113</v>
+        <v>2792</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3133519650</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>2800</v>
@@ -8984,10 +8978,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="4" t="s">
-        <v>2791</v>
+        <v>2793</v>
       </c>
       <c r="B14" s="4">
-        <v>3103914892</v>
+        <v>3203612280</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>2800</v>
@@ -8996,10 +8990,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="4" t="s">
-        <v>2792</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4">
-        <v>3133519650</v>
+        <v>3103319459</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>2800</v>
@@ -9008,10 +9002,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>2793</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4">
-        <v>3203612280</v>
+        <v>3213605848</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>2800</v>
@@ -9020,10 +9014,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" s="4">
-        <v>3103319459</v>
+        <v>3133523454</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>2800</v>
@@ -9032,10 +9026,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B18" s="4">
-        <v>3213605848</v>
+        <v>3203396742</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>2800</v>
@@ -9044,10 +9038,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>11</v>
+        <v>2794</v>
       </c>
       <c r="B19" s="4">
-        <v>3133523454</v>
+        <v>3105672288</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>2800</v>
@@ -9056,10 +9050,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>2795</v>
       </c>
       <c r="B20" s="4">
-        <v>3203396742</v>
+        <v>3152092988</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>2800</v>
@@ -9068,10 +9062,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>2794</v>
+        <v>32</v>
       </c>
       <c r="B21" s="4">
-        <v>3105672288</v>
+        <v>3103269000</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>2800</v>
@@ -9080,10 +9074,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>2795</v>
+        <v>2796</v>
       </c>
       <c r="B22" s="4">
-        <v>3152092988</v>
+        <v>3103064593</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>2800</v>
@@ -9092,10 +9086,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>32</v>
+        <v>2797</v>
       </c>
       <c r="B23" s="4">
-        <v>3103269000</v>
+        <v>3124011214</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>2800</v>
@@ -9104,10 +9098,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>2796</v>
+        <v>2798</v>
       </c>
       <c r="B24" s="4">
-        <v>3103064593</v>
+        <v>3124158907</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>2800</v>
@@ -9116,10 +9110,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>2797</v>
+        <v>2799</v>
       </c>
       <c r="B25" s="4">
-        <v>3124011214</v>
+        <v>3114579876</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>2800</v>
@@ -9128,52 +9122,28 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>2798</v>
+        <v>188</v>
       </c>
       <c r="B26" s="4">
-        <v>3124158907</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>2800</v>
-      </c>
+        <v>3102214654</v>
+      </c>
+      <c r="C26" s="4"/>
       <c r="D26" s="4"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="4" t="s">
-        <v>2799</v>
-      </c>
-      <c r="B27" s="4">
-        <v>3114579876</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>2800</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
       <c r="D27" s="4"/>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B28" s="4">
-        <v>3102214654</v>
-      </c>
+    <row r="28" spans="1:4" ht="22.5" customHeight="1">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" ht="22.5" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="1048570" spans="3:3">
-      <c r="C1048570" t="s">
+    <row r="1048568" spans="3:3">
+      <c r="C1048568" t="s">
         <v>2800</v>
       </c>
     </row>
